--- a/week-01/digital_storytelling_sales_dataset.xlsx
+++ b/week-01/digital_storytelling_sales_dataset.xlsx
@@ -1,38 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/ilee_my_yearupunited_org/Documents/Documents/PracticeExercises/week-01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F717A3C7-E657-4B10-9CBB-C81CAB24D64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="212" documentId="8_{F717A3C7-E657-4B10-9CBB-C81CAB24D64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BACE507D-34FE-4E97-A979-3FB78AD0B2AC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
-    <sheet name="Retail Sales Data" sheetId="1" r:id="rId3"/>
+    <sheet name="Visuals" sheetId="4" r:id="rId1"/>
+    <sheet name="Retail Sales Data" sheetId="1" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_digital_storytelling_sales_dataset.xlsxSalesData1" hidden="1">SalesData[]</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="42" r:id="rId4"/>
-    <pivotCache cacheId="38" r:id="rId5"/>
+    <pivotCache cacheId="8" r:id="rId3"/>
   </pivotCaches>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
-      <x15:dataModel>
-        <x15:modelTables>
-          <x15:modelTable id="SalesData" name="SalesData" connection="WorksheetConnection_digital_storytelling_sales_dataset.xlsx!SalesData"/>
-        </x15:modelTables>
-      </x15:dataModel>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -48,31 +36,8 @@
 </workbook>
 </file>
 
-<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{90E95A7E-2DC7-4720-9496-D589A0D352DC}" keepAlive="1" name="ThisWorkbookDataModel" description="Data Model" type="5" refreshedVersion="8" minRefreshableVersion="5" background="1">
-    <dbPr connection="Data Model Connection" command="Model" commandType="1"/>
-    <olapPr sendLocale="1" rowDrillCount="1000"/>
-    <extLst>
-      <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
-        <x15:connection id="" model="1"/>
-      </ext>
-    </extLst>
-  </connection>
-  <connection id="2" xr16:uid="{DD2A25D9-F90E-49EC-AA8C-FBF37F7DF19D}" name="WorksheetConnection_digital_storytelling_sales_dataset.xlsx!SalesData" type="102" refreshedVersion="8" minRefreshableVersion="5">
-    <extLst>
-      <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
-        <x15:connection id="SalesData" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_digital_storytelling_sales_dataset.xlsxSalesData1"/>
-        </x15:connection>
-      </ext>
-    </extLst>
-  </connection>
-</connections>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="125">
   <si>
     <t>Order ID</t>
   </si>
@@ -434,13 +399,20 @@
     <t>Match</t>
   </si>
   <si>
-    <t>Row Labels</t>
-  </si>
-  <si>
     <t>Grand Total</t>
   </si>
   <si>
     <t>Sum of Total Sales</t>
+  </si>
+  <si>
+    <t>Regions</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top Customer
+</t>
   </si>
 </sst>
 </file>
@@ -448,7 +420,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -481,28 +453,28 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -515,6 +487,3403 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="104"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="4"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[digital_storytelling_sales_dataset.xlsx]Visuals!PivotTable2</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mj-lt"/>
+                <a:ea typeface="+mj-ea"/>
+                <a:cs typeface="+mj-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>West</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> to lead all Regions in Revenue</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mj-lt"/>
+              <a:ea typeface="+mj-ea"/>
+              <a:cs typeface="+mj-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="8"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="1"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:bar3DChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Visuals!$B$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-DBA4-4999-B755-6B9F7F9219BA}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-DBA4-4999-B755-6B9F7F9219BA}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-DBA4-4999-B755-6B9F7F9219BA}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Visuals!$A$14:$A$18</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Visuals!$B$14:$B$18</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>49560</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>55200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>56690</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>59610</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DBA4-4999-B755-6B9F7F9219BA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:shape val="box"/>
+        <c:axId val="202859840"/>
+        <c:axId val="202868480"/>
+        <c:axId val="0"/>
+      </c:bar3DChart>
+      <c:catAx>
+        <c:axId val="202859840"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="202868480"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="202868480"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="202859840"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[digital_storytelling_sales_dataset.xlsx]Visuals!PivotTable4</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Laptops</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Leading in Product Sales</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Visuals!$B$23</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Visuals!$A$24:$A$32</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Laptop</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Phone</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Desk</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Monitor</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Tablet</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Printer</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Bookshelf</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Chair</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Visuals!$B$24:$B$32</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>61200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>29750</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>21600</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18750</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15600</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6960</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C304-4D68-97E5-638B1CB9CD56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1701202624"/>
+        <c:axId val="1701206464"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1701202624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1701206464"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1701206464"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1701202624"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[digital_storytelling_sales_dataset.xlsx]Visuals!PivotTable5</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Technology</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> has the Leading Percentage of Sales</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="0.12777777777777777"/>
+              <c:y val="-4.1666666666666664E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="-0.16944444444444445"/>
+              <c:y val="8.7962962962962965E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Visuals!$B$36</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-24E2-4B2A-B803-D6D4C96AA327}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-24E2-4B2A-B803-D6D4C96AA327}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.12777777777777777"/>
+                  <c:y val="-4.1666666666666664E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-24E2-4B2A-B803-D6D4C96AA327}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.16944444444444445"/>
+                  <c:y val="8.7962962962962965E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-24E2-4B2A-B803-D6D4C96AA327}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Visuals!$A$37:$A$39</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Furniture</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Technology</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Visuals!$B$37:$B$39</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.23663258843752827</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.76336741156247168</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-24E2-4B2A-B803-D6D4C96AA327}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="75"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
+  <a:schemeClr val="accent2"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="296">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="0" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="38100" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="8"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="major">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="2000" b="0" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>601986</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BBE751A-B4DF-D710-470E-763DCA6F9CC2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EAD17E6-9E0B-90B9-EA62-4044C62DC073}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CB1D398-AABA-3E3A-B8FB-90D50890D6E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -550,7 +3919,10 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Category" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="2">
+        <s v="Technology"/>
+        <s v="Furniture"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Customer" numFmtId="0">
       <sharedItems count="20">
@@ -579,13 +3951,13 @@
     <cacheField name="Units Sold" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="8"/>
     </cacheField>
-    <cacheField name="Unit Price" numFmtId="165">
+    <cacheField name="Unit Price" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="120" maxValue="900"/>
     </cacheField>
-    <cacheField name="Total Sales" numFmtId="165">
+    <cacheField name="Total Sales" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="120" maxValue="7200"/>
     </cacheField>
-    <cacheField name="Check Sales" numFmtId="165">
+    <cacheField name="Check Sales" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="120" maxValue="7200"/>
     </cacheField>
     <cacheField name="Match" numFmtId="0">
@@ -600,69 +3972,6 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="idasha lee" refreshedDate="46314.773844791664" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{78853491-D801-48BC-B23F-0FD1AD0AC20C}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="2">
-    <cacheField name="[Measures].[Sum of Total Sales]" caption="Sum of Total Sales" numFmtId="0" hierarchy="13" level="32767"/>
-    <cacheField name="[SalesData].[Region].[Region]" caption="Region" numFmtId="0" hierarchy="2" level="1">
-      <sharedItems count="4">
-        <s v="East"/>
-        <s v="North"/>
-        <s v="South"/>
-        <s v="West"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="14">
-    <cacheHierarchy uniqueName="[SalesData].[Order ID]" caption="Order ID" attribute="1" defaultMemberUniqueName="[SalesData].[Order ID].[All]" allUniqueName="[SalesData].[Order ID].[All]" dimensionUniqueName="[SalesData]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[SalesData].[Date]" caption="Date" attribute="1" defaultMemberUniqueName="[SalesData].[Date].[All]" allUniqueName="[SalesData].[Date].[All]" dimensionUniqueName="[SalesData]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[SalesData].[Region]" caption="Region" attribute="1" defaultMemberUniqueName="[SalesData].[Region].[All]" allUniqueName="[SalesData].[Region].[All]" dimensionUniqueName="[SalesData]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[SalesData].[Product]" caption="Product" attribute="1" defaultMemberUniqueName="[SalesData].[Product].[All]" allUniqueName="[SalesData].[Product].[All]" dimensionUniqueName="[SalesData]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[SalesData].[Category]" caption="Category" attribute="1" defaultMemberUniqueName="[SalesData].[Category].[All]" allUniqueName="[SalesData].[Category].[All]" dimensionUniqueName="[SalesData]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[SalesData].[Customer]" caption="Customer" attribute="1" defaultMemberUniqueName="[SalesData].[Customer].[All]" allUniqueName="[SalesData].[Customer].[All]" dimensionUniqueName="[SalesData]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[SalesData].[Units Sold]" caption="Units Sold" attribute="1" defaultMemberUniqueName="[SalesData].[Units Sold].[All]" allUniqueName="[SalesData].[Units Sold].[All]" dimensionUniqueName="[SalesData]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[SalesData].[Unit Price]" caption="Unit Price" attribute="1" defaultMemberUniqueName="[SalesData].[Unit Price].[All]" allUniqueName="[SalesData].[Unit Price].[All]" dimensionUniqueName="[SalesData]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[SalesData].[Total Sales]" caption="Total Sales" attribute="1" defaultMemberUniqueName="[SalesData].[Total Sales].[All]" allUniqueName="[SalesData].[Total Sales].[All]" dimensionUniqueName="[SalesData]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[SalesData].[Check Sales]" caption="Check Sales" attribute="1" defaultMemberUniqueName="[SalesData].[Check Sales].[All]" allUniqueName="[SalesData].[Check Sales].[All]" dimensionUniqueName="[SalesData]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[SalesData].[Match]" caption="Match" attribute="1" defaultMemberUniqueName="[SalesData].[Match].[All]" allUniqueName="[SalesData].[Match].[All]" dimensionUniqueName="[SalesData]" displayFolder="" count="0" memberValueDatatype="11" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count SalesData]" caption="__XL_Count SalesData" measure="1" displayFolder="" measureGroup="SalesData" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Total Sales]" caption="Sum of Total Sales" measure="1" displayFolder="" measureGroup="SalesData" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="8"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="2">
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="SalesData" uniqueName="[SalesData]" caption="SalesData"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="SalesData" caption="SalesData"/>
-  </measureGroups>
-  <maps count="1">
-    <map measureGroup="0" dimension="1"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="120">
   <r>
@@ -670,7 +3979,7 @@
     <s v="2025-04-21"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="2"/>
     <n v="900"/>
@@ -683,7 +3992,7 @@
     <s v="2025-03-21"/>
     <x v="1"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="1"/>
     <n v="8"/>
     <n v="300"/>
@@ -696,7 +4005,7 @@
     <s v="2025-01-18"/>
     <x v="1"/>
     <x v="2"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="2"/>
     <n v="6"/>
     <n v="350"/>
@@ -709,7 +4018,7 @@
     <s v="2025-04-28"/>
     <x v="0"/>
     <x v="2"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="3"/>
     <n v="2"/>
     <n v="350"/>
@@ -722,7 +4031,7 @@
     <s v="2025-03-19"/>
     <x v="2"/>
     <x v="3"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="4"/>
     <n v="5"/>
     <n v="250"/>
@@ -735,7 +4044,7 @@
     <s v="2025-04-19"/>
     <x v="3"/>
     <x v="4"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="2"/>
     <n v="1"/>
     <n v="200"/>
@@ -748,7 +4057,7 @@
     <s v="2025-02-03"/>
     <x v="1"/>
     <x v="4"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="5"/>
     <n v="7"/>
     <n v="200"/>
@@ -761,7 +4070,7 @@
     <s v="2025-04-02"/>
     <x v="0"/>
     <x v="4"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="3"/>
     <n v="5"/>
     <n v="200"/>
@@ -774,7 +4083,7 @@
     <s v="2025-02-10"/>
     <x v="2"/>
     <x v="5"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="4"/>
     <n v="5"/>
     <n v="120"/>
@@ -787,7 +4096,7 @@
     <s v="2025-02-25"/>
     <x v="2"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="1"/>
     <n v="7"/>
     <n v="300"/>
@@ -800,7 +4109,7 @@
     <s v="2025-03-17"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="6"/>
     <n v="1"/>
     <n v="900"/>
@@ -813,7 +4122,7 @@
     <s v="2025-03-30"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="7"/>
     <n v="7"/>
     <n v="900"/>
@@ -826,7 +4135,7 @@
     <s v="2025-04-08"/>
     <x v="1"/>
     <x v="0"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="8"/>
     <n v="7"/>
     <n v="900"/>
@@ -839,7 +4148,7 @@
     <s v="2025-03-22"/>
     <x v="3"/>
     <x v="4"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="9"/>
     <n v="6"/>
     <n v="200"/>
@@ -852,7 +4161,7 @@
     <s v="2025-03-25"/>
     <x v="0"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="3"/>
     <n v="7"/>
     <n v="300"/>
@@ -865,7 +4174,7 @@
     <s v="2025-03-19"/>
     <x v="3"/>
     <x v="0"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="10"/>
     <n v="5"/>
     <n v="900"/>
@@ -878,7 +4187,7 @@
     <s v="2025-03-24"/>
     <x v="2"/>
     <x v="6"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="11"/>
     <n v="2"/>
     <n v="600"/>
@@ -891,7 +4200,7 @@
     <s v="2025-03-15"/>
     <x v="2"/>
     <x v="6"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="3"/>
     <n v="4"/>
     <n v="600"/>
@@ -904,7 +4213,7 @@
     <s v="2025-04-27"/>
     <x v="3"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="3"/>
     <n v="3"/>
     <n v="300"/>
@@ -917,7 +4226,7 @@
     <s v="2025-03-22"/>
     <x v="1"/>
     <x v="6"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="6"/>
     <n v="2"/>
     <n v="600"/>
@@ -930,7 +4239,7 @@
     <s v="2025-01-07"/>
     <x v="2"/>
     <x v="5"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="12"/>
     <n v="3"/>
     <n v="120"/>
@@ -943,7 +4252,7 @@
     <s v="2025-02-06"/>
     <x v="1"/>
     <x v="4"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="7"/>
     <n v="200"/>
@@ -956,7 +4265,7 @@
     <s v="2025-04-04"/>
     <x v="0"/>
     <x v="2"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="5"/>
     <n v="8"/>
     <n v="350"/>
@@ -969,7 +4278,7 @@
     <s v="2025-04-04"/>
     <x v="1"/>
     <x v="3"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="13"/>
     <n v="4"/>
     <n v="250"/>
@@ -982,7 +4291,7 @@
     <s v="2025-03-25"/>
     <x v="2"/>
     <x v="6"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="13"/>
     <n v="7"/>
     <n v="600"/>
@@ -995,7 +4304,7 @@
     <s v="2025-02-05"/>
     <x v="2"/>
     <x v="4"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="7"/>
     <n v="3"/>
     <n v="200"/>
@@ -1008,7 +4317,7 @@
     <s v="2025-03-16"/>
     <x v="1"/>
     <x v="7"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="13"/>
     <n v="7"/>
     <n v="400"/>
@@ -1021,7 +4330,7 @@
     <s v="2025-04-01"/>
     <x v="3"/>
     <x v="5"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="7"/>
     <n v="2"/>
     <n v="120"/>
@@ -1034,7 +4343,7 @@
     <s v="2025-01-08"/>
     <x v="0"/>
     <x v="7"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="8"/>
     <n v="7"/>
     <n v="400"/>
@@ -1047,7 +4356,7 @@
     <s v="2025-03-03"/>
     <x v="3"/>
     <x v="3"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="5"/>
     <n v="8"/>
     <n v="250"/>
@@ -1060,7 +4369,7 @@
     <s v="2025-01-27"/>
     <x v="1"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="14"/>
     <n v="3"/>
     <n v="300"/>
@@ -1073,7 +4382,7 @@
     <s v="2025-03-06"/>
     <x v="2"/>
     <x v="4"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="12"/>
     <n v="6"/>
     <n v="200"/>
@@ -1086,7 +4395,7 @@
     <s v="2025-01-19"/>
     <x v="2"/>
     <x v="4"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="15"/>
     <n v="2"/>
     <n v="200"/>
@@ -1099,7 +4408,7 @@
     <s v="2025-03-14"/>
     <x v="2"/>
     <x v="0"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="3"/>
     <n v="6"/>
     <n v="900"/>
@@ -1112,7 +4421,7 @@
     <s v="2025-01-13"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="8"/>
     <n v="6"/>
     <n v="900"/>
@@ -1125,7 +4434,7 @@
     <s v="2025-02-01"/>
     <x v="1"/>
     <x v="3"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="13"/>
     <n v="8"/>
     <n v="250"/>
@@ -1138,7 +4447,7 @@
     <s v="2025-04-17"/>
     <x v="3"/>
     <x v="3"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="5"/>
     <n v="3"/>
     <n v="250"/>
@@ -1151,7 +4460,7 @@
     <s v="2025-03-15"/>
     <x v="0"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="16"/>
     <n v="2"/>
     <n v="300"/>
@@ -1164,7 +4473,7 @@
     <s v="2025-03-14"/>
     <x v="1"/>
     <x v="2"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="15"/>
     <n v="8"/>
     <n v="350"/>
@@ -1177,7 +4486,7 @@
     <s v="2025-01-24"/>
     <x v="2"/>
     <x v="3"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="5"/>
     <n v="2"/>
     <n v="250"/>
@@ -1190,7 +4499,7 @@
     <s v="2025-01-21"/>
     <x v="2"/>
     <x v="6"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="17"/>
     <n v="7"/>
     <n v="600"/>
@@ -1203,7 +4512,7 @@
     <s v="2025-03-19"/>
     <x v="0"/>
     <x v="3"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="3"/>
     <n v="5"/>
     <n v="250"/>
@@ -1216,7 +4525,7 @@
     <s v="2025-03-30"/>
     <x v="0"/>
     <x v="3"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="16"/>
     <n v="3"/>
     <n v="250"/>
@@ -1229,7 +4538,7 @@
     <s v="2025-02-26"/>
     <x v="3"/>
     <x v="7"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="1"/>
     <n v="2"/>
     <n v="400"/>
@@ -1242,7 +4551,7 @@
     <s v="2025-01-13"/>
     <x v="3"/>
     <x v="0"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="8"/>
     <n v="1"/>
     <n v="900"/>
@@ -1255,7 +4564,7 @@
     <s v="2025-01-30"/>
     <x v="1"/>
     <x v="0"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="18"/>
     <n v="6"/>
     <n v="900"/>
@@ -1268,7 +4577,7 @@
     <s v="2025-02-19"/>
     <x v="2"/>
     <x v="2"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="10"/>
     <n v="7"/>
     <n v="350"/>
@@ -1281,7 +4590,7 @@
     <s v="2025-04-02"/>
     <x v="2"/>
     <x v="4"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="5"/>
     <n v="3"/>
     <n v="200"/>
@@ -1294,7 +4603,7 @@
     <s v="2025-01-26"/>
     <x v="3"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="18"/>
     <n v="1"/>
     <n v="300"/>
@@ -1307,7 +4616,7 @@
     <s v="2025-02-13"/>
     <x v="0"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="19"/>
     <n v="8"/>
     <n v="300"/>
@@ -1320,7 +4629,7 @@
     <s v="2025-03-30"/>
     <x v="2"/>
     <x v="6"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="18"/>
     <n v="6"/>
     <n v="600"/>
@@ -1333,7 +4642,7 @@
     <s v="2025-02-06"/>
     <x v="3"/>
     <x v="6"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="15"/>
     <n v="8"/>
     <n v="600"/>
@@ -1346,7 +4655,7 @@
     <s v="2025-03-13"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="13"/>
     <n v="2"/>
     <n v="120"/>
@@ -1359,7 +4668,7 @@
     <s v="2025-01-19"/>
     <x v="3"/>
     <x v="0"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="7"/>
     <n v="2"/>
     <n v="900"/>
@@ -1372,7 +4681,7 @@
     <s v="2025-01-29"/>
     <x v="2"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="11"/>
     <n v="6"/>
     <n v="300"/>
@@ -1385,7 +4694,7 @@
     <s v="2025-01-04"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="6"/>
     <n v="6"/>
     <n v="120"/>
@@ -1398,7 +4707,7 @@
     <s v="2025-01-26"/>
     <x v="1"/>
     <x v="6"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="2"/>
     <n v="7"/>
     <n v="600"/>
@@ -1411,7 +4720,7 @@
     <s v="2025-04-25"/>
     <x v="3"/>
     <x v="7"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="15"/>
     <n v="7"/>
     <n v="400"/>
@@ -1424,7 +4733,7 @@
     <s v="2025-04-23"/>
     <x v="0"/>
     <x v="2"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="2"/>
     <n v="3"/>
     <n v="350"/>
@@ -1437,7 +4746,7 @@
     <s v="2025-03-08"/>
     <x v="2"/>
     <x v="6"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="13"/>
     <n v="4"/>
     <n v="600"/>
@@ -1450,7 +4759,7 @@
     <s v="2025-01-08"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="5"/>
     <n v="8"/>
     <n v="120"/>
@@ -1463,7 +4772,7 @@
     <s v="2025-04-16"/>
     <x v="2"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="18"/>
     <n v="2"/>
     <n v="300"/>
@@ -1476,7 +4785,7 @@
     <s v="2025-03-21"/>
     <x v="0"/>
     <x v="2"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="6"/>
     <n v="3"/>
     <n v="350"/>
@@ -1489,7 +4798,7 @@
     <s v="2025-04-07"/>
     <x v="0"/>
     <x v="3"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="16"/>
     <n v="2"/>
     <n v="250"/>
@@ -1502,7 +4811,7 @@
     <s v="2025-01-14"/>
     <x v="0"/>
     <x v="7"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="16"/>
     <n v="8"/>
     <n v="400"/>
@@ -1515,7 +4824,7 @@
     <s v="2025-01-02"/>
     <x v="2"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="4"/>
     <n v="300"/>
@@ -1528,7 +4837,7 @@
     <s v="2025-03-04"/>
     <x v="3"/>
     <x v="7"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="8"/>
     <n v="400"/>
@@ -1541,7 +4850,7 @@
     <s v="2025-04-14"/>
     <x v="3"/>
     <x v="7"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="4"/>
     <n v="400"/>
@@ -1554,7 +4863,7 @@
     <s v="2025-03-15"/>
     <x v="3"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="17"/>
     <n v="1"/>
     <n v="300"/>
@@ -1567,7 +4876,7 @@
     <s v="2025-03-30"/>
     <x v="2"/>
     <x v="3"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="1"/>
     <n v="1"/>
     <n v="250"/>
@@ -1580,7 +4889,7 @@
     <s v="2025-02-09"/>
     <x v="0"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="16"/>
     <n v="3"/>
     <n v="300"/>
@@ -1593,7 +4902,7 @@
     <s v="2025-04-27"/>
     <x v="3"/>
     <x v="5"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="0"/>
     <n v="2"/>
     <n v="120"/>
@@ -1606,7 +4915,7 @@
     <s v="2025-02-02"/>
     <x v="1"/>
     <x v="6"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="16"/>
     <n v="4"/>
     <n v="600"/>
@@ -1619,7 +4928,7 @@
     <s v="2025-03-09"/>
     <x v="0"/>
     <x v="4"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="11"/>
     <n v="8"/>
     <n v="200"/>
@@ -1632,7 +4941,7 @@
     <s v="2025-01-08"/>
     <x v="0"/>
     <x v="3"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="15"/>
     <n v="5"/>
     <n v="250"/>
@@ -1645,7 +4954,7 @@
     <s v="2025-02-22"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="5"/>
     <n v="3"/>
     <n v="900"/>
@@ -1658,7 +4967,7 @@
     <s v="2025-03-10"/>
     <x v="3"/>
     <x v="5"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="13"/>
     <n v="8"/>
     <n v="120"/>
@@ -1671,7 +4980,7 @@
     <s v="2025-02-15"/>
     <x v="3"/>
     <x v="2"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="8"/>
     <n v="350"/>
@@ -1684,7 +4993,7 @@
     <s v="2025-01-16"/>
     <x v="3"/>
     <x v="2"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="16"/>
     <n v="3"/>
     <n v="350"/>
@@ -1697,7 +5006,7 @@
     <s v="2025-02-24"/>
     <x v="2"/>
     <x v="0"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="3"/>
     <n v="2"/>
     <n v="900"/>
@@ -1710,7 +5019,7 @@
     <s v="2025-01-16"/>
     <x v="3"/>
     <x v="5"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="12"/>
     <n v="6"/>
     <n v="120"/>
@@ -1723,7 +5032,7 @@
     <s v="2025-03-07"/>
     <x v="2"/>
     <x v="7"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="15"/>
     <n v="8"/>
     <n v="400"/>
@@ -1736,7 +5045,7 @@
     <s v="2025-03-18"/>
     <x v="2"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="16"/>
     <n v="4"/>
     <n v="300"/>
@@ -1749,7 +5058,7 @@
     <s v="2025-02-04"/>
     <x v="3"/>
     <x v="3"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="10"/>
     <n v="4"/>
     <n v="250"/>
@@ -1762,7 +5071,7 @@
     <s v="2025-01-11"/>
     <x v="3"/>
     <x v="4"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="11"/>
     <n v="6"/>
     <n v="200"/>
@@ -1775,7 +5084,7 @@
     <s v="2025-03-14"/>
     <x v="0"/>
     <x v="7"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="2"/>
     <n v="3"/>
     <n v="400"/>
@@ -1788,7 +5097,7 @@
     <s v="2025-04-26"/>
     <x v="1"/>
     <x v="2"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="12"/>
     <n v="3"/>
     <n v="350"/>
@@ -1801,7 +5110,7 @@
     <s v="2025-02-02"/>
     <x v="2"/>
     <x v="2"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="18"/>
     <n v="8"/>
     <n v="350"/>
@@ -1814,7 +5123,7 @@
     <s v="2025-02-02"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="8"/>
     <n v="1"/>
     <n v="120"/>
@@ -1827,7 +5136,7 @@
     <s v="2025-02-28"/>
     <x v="1"/>
     <x v="5"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="15"/>
     <n v="1"/>
     <n v="120"/>
@@ -1840,7 +5149,7 @@
     <s v="2025-01-03"/>
     <x v="1"/>
     <x v="3"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="1"/>
     <n v="1"/>
     <n v="250"/>
@@ -1853,7 +5162,7 @@
     <s v="2025-01-19"/>
     <x v="2"/>
     <x v="6"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="10"/>
     <n v="5"/>
     <n v="600"/>
@@ -1866,7 +5175,7 @@
     <s v="2025-01-28"/>
     <x v="0"/>
     <x v="4"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="4"/>
     <n v="8"/>
     <n v="200"/>
@@ -1879,7 +5188,7 @@
     <s v="2025-04-22"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="15"/>
     <n v="3"/>
     <n v="900"/>
@@ -1892,7 +5201,7 @@
     <s v="2025-03-04"/>
     <x v="3"/>
     <x v="2"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="9"/>
     <n v="7"/>
     <n v="350"/>
@@ -1905,7 +5214,7 @@
     <s v="2025-01-28"/>
     <x v="0"/>
     <x v="4"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="9"/>
     <n v="3"/>
     <n v="200"/>
@@ -1918,7 +5227,7 @@
     <s v="2025-03-08"/>
     <x v="3"/>
     <x v="5"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="14"/>
     <n v="4"/>
     <n v="120"/>
@@ -1931,7 +5240,7 @@
     <s v="2025-03-27"/>
     <x v="0"/>
     <x v="0"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="17"/>
     <n v="3"/>
     <n v="900"/>
@@ -1944,7 +5253,7 @@
     <s v="2025-01-09"/>
     <x v="2"/>
     <x v="0"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="15"/>
     <n v="2"/>
     <n v="900"/>
@@ -1957,7 +5266,7 @@
     <s v="2025-04-04"/>
     <x v="0"/>
     <x v="5"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="7"/>
     <n v="8"/>
     <n v="120"/>
@@ -1970,7 +5279,7 @@
     <s v="2025-01-13"/>
     <x v="1"/>
     <x v="4"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="18"/>
     <n v="5"/>
     <n v="200"/>
@@ -1983,7 +5292,7 @@
     <s v="2025-03-21"/>
     <x v="3"/>
     <x v="4"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="5"/>
     <n v="3"/>
     <n v="200"/>
@@ -1996,7 +5305,7 @@
     <s v="2025-01-18"/>
     <x v="3"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="2"/>
     <n v="8"/>
     <n v="300"/>
@@ -2009,7 +5318,7 @@
     <s v="2025-01-16"/>
     <x v="1"/>
     <x v="0"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="7"/>
     <n v="8"/>
     <n v="900"/>
@@ -2022,7 +5331,7 @@
     <s v="2025-02-25"/>
     <x v="3"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="13"/>
     <n v="4"/>
     <n v="300"/>
@@ -2035,7 +5344,7 @@
     <s v="2025-01-04"/>
     <x v="3"/>
     <x v="0"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="11"/>
     <n v="4"/>
     <n v="900"/>
@@ -2048,7 +5357,7 @@
     <s v="2025-01-24"/>
     <x v="0"/>
     <x v="3"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="8"/>
     <n v="4"/>
     <n v="250"/>
@@ -2061,7 +5370,7 @@
     <s v="2025-03-28"/>
     <x v="2"/>
     <x v="6"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="3"/>
     <n v="8"/>
     <n v="600"/>
@@ -2074,7 +5383,7 @@
     <s v="2025-01-06"/>
     <x v="3"/>
     <x v="2"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="7"/>
     <n v="350"/>
@@ -2087,7 +5396,7 @@
     <s v="2025-02-26"/>
     <x v="0"/>
     <x v="4"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="9"/>
     <n v="5"/>
     <n v="200"/>
@@ -2100,7 +5409,7 @@
     <s v="2025-02-27"/>
     <x v="2"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="11"/>
     <n v="7"/>
     <n v="300"/>
@@ -2113,7 +5422,7 @@
     <s v="2025-02-08"/>
     <x v="3"/>
     <x v="3"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="17"/>
     <n v="8"/>
     <n v="250"/>
@@ -2126,7 +5435,7 @@
     <s v="2025-01-13"/>
     <x v="3"/>
     <x v="6"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="18"/>
     <n v="8"/>
     <n v="600"/>
@@ -2139,7 +5448,7 @@
     <s v="2025-03-08"/>
     <x v="2"/>
     <x v="1"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="7"/>
     <n v="2"/>
     <n v="300"/>
@@ -2152,7 +5461,7 @@
     <s v="2025-04-26"/>
     <x v="1"/>
     <x v="5"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="19"/>
     <n v="2"/>
     <n v="120"/>
@@ -2165,7 +5474,7 @@
     <s v="2025-04-19"/>
     <x v="1"/>
     <x v="3"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="12"/>
     <n v="8"/>
     <n v="250"/>
@@ -2178,7 +5487,7 @@
     <s v="2025-01-04"/>
     <x v="1"/>
     <x v="2"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="8"/>
     <n v="4"/>
     <n v="350"/>
@@ -2191,7 +5500,7 @@
     <s v="2025-04-04"/>
     <x v="2"/>
     <x v="3"/>
-    <s v="Technology"/>
+    <x v="0"/>
     <x v="12"/>
     <n v="4"/>
     <n v="250"/>
@@ -2204,7 +5513,7 @@
     <s v="2025-02-01"/>
     <x v="3"/>
     <x v="2"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="16"/>
     <n v="7"/>
     <n v="350"/>
@@ -2217,7 +5526,7 @@
     <s v="2025-03-13"/>
     <x v="0"/>
     <x v="2"/>
-    <s v="Furniture"/>
+    <x v="1"/>
     <x v="7"/>
     <n v="1"/>
     <n v="350"/>
@@ -2229,92 +5538,15 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{648A6BC9-F382-4FBA-9C3D-1A0EFADDE75E}" name="PivotTable8" cacheId="38" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" allDrilled="1" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="0" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotHierarchies count="14">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="2"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_digital_storytelling_sales_dataset.xlsx!SalesData">
-        <x15:activeTabTopLevelEntity name="[SalesData]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{140A5A2B-AFB1-437D-90E2-A2886B74E538}" name="PivotTable10" cacheId="42" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E7:E28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1E61E9B-B5D5-44D3-B907-F4EECC3FF2D0}" name="PivotTable6" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Top Customer_x000a_">
+  <location ref="A44:B46" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" measureFilter="1">
       <items count="21">
         <item x="4"/>
         <item x="10"/>
@@ -2340,74 +5572,17 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="5"/>
   </rowFields>
-  <rowItems count="21">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
+  <rowItems count="2">
     <i>
       <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
     </i>
     <i t="grand">
       <x/>
@@ -2416,6 +5591,107 @@
   <colItems count="1">
     <i/>
   </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="5" type="count" evalOrder="-1" id="2" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="1" filterVal="1"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{447D4A10-550B-42C2-AA12-30A74151AB62}" name="PivotTable5" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Category">
+  <location ref="A36:B39" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -2429,13 +5705,13 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04F8818E-9E16-4A5E-86A7-CAF0ED7BF623}" name="PivotTable9" cacheId="42" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B14:C23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47FE4132-C5AB-431D-926D-A3B2E229CF18}" name="PivotTable4" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Products">
+  <location ref="A23:B32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="9">
         <item x="4"/>
         <item x="5"/>
@@ -2447,13 +5723,22 @@
         <item x="7"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -2461,28 +5746,28 @@
   </rowFields>
   <rowItems count="9">
     <i>
-      <x/>
+      <x v="3"/>
     </i>
     <i>
-      <x v="1"/>
+      <x v="5"/>
     </i>
     <i>
       <x v="2"/>
     </i>
     <i>
-      <x v="3"/>
-    </i>
-    <i>
       <x v="4"/>
     </i>
     <i>
-      <x v="5"/>
+      <x v="7"/>
     </i>
     <i>
       <x v="6"/>
     </i>
     <i>
-      <x v="7"/>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -2492,8 +5777,19 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -2507,12 +5803,12 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3FED62C0-B503-435B-BF8A-782A5D6D947A}" name="PivotTable7" cacheId="42" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00E69FA9-096F-43FA-A96B-ACFF8571859C}" name="PivotTable2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" rowHeaderCaption="Regions">
+  <location ref="A13:B18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
       <items count="5">
         <item x="1"/>
         <item x="3"/>
@@ -2520,14 +5816,23 @@
         <item x="2"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -2538,10 +5843,10 @@
       <x/>
     </i>
     <i>
-      <x v="1"/>
+      <x v="2"/>
     </i>
     <i>
-      <x v="2"/>
+      <x v="1"/>
     </i>
     <i>
       <x v="3"/>
@@ -2554,7 +5859,91 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{293EDDD3-FB3A-4EAB-87B9-9904BB6E9F33}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -2579,12 +5968,12 @@
     <tableColumn id="5" xr3:uid="{3F518EF9-08EE-48C0-84B2-55642AAD0B05}" name="Category"/>
     <tableColumn id="6" xr3:uid="{EEA98EF4-AD88-4467-AFB1-F017E1FAA4BF}" name="Customer"/>
     <tableColumn id="7" xr3:uid="{42AA311B-C619-432D-BB7E-0F09388915DB}" name="Units Sold"/>
-    <tableColumn id="8" xr3:uid="{97A047E4-A54C-4D3B-B7CF-E78906DF5870}" name="Unit Price" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{9E90114F-48D5-4D8D-BD58-88FA7994D226}" name="Total Sales" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{FB167FA7-FF5E-4E57-8142-FC2D0054588A}" name="Check Sales" dataDxfId="0">
+    <tableColumn id="8" xr3:uid="{97A047E4-A54C-4D3B-B7CF-E78906DF5870}" name="Unit Price" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{9E90114F-48D5-4D8D-BD58-88FA7994D226}" name="Total Sales" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{FB167FA7-FF5E-4E57-8142-FC2D0054588A}" name="Check Sales" dataDxfId="1">
       <calculatedColumnFormula>G2*H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{4EBAA8A9-7A8C-43C4-AC62-ED1473FEE7CF}" name="Match" dataDxfId="3">
+    <tableColumn id="11" xr3:uid="{4EBAA8A9-7A8C-43C4-AC62-ED1473FEE7CF}" name="Match" dataDxfId="0">
       <calculatedColumnFormula>SalesData[[#This Row],[Check Sales]]=SalesData[[#This Row],[Total Sales]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2876,298 +6265,220 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8766EE60-A061-40EC-8444-E4C8C2B05C7D}">
-  <dimension ref="A3:B8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2C7B0F5-3B8D-414B-9151-665A338F6902}">
+  <dimension ref="A3:B46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="1">
+        <f>SUM(SalesData[Total Sales])</f>
+        <v>221060</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>221060</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1">
+        <v>49560</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="1">
+        <v>55200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="1">
+        <v>56690</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1">
+        <v>59610</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="4">
-        <v>49560</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="4">
-        <v>56690</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="4">
-        <v>55200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="4">
-        <v>59610</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="B18" s="1">
+        <v>221060</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B23" t="s">
         <v>121</v>
       </c>
-      <c r="B8" s="4">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="1">
+        <v>61200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="1">
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="1">
+        <v>29750</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="1">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="1">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="1">
+        <v>18750</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="1">
+        <v>15600</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="1">
+        <v>6960</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B32" s="1">
         <v>221060</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" s="4">
+        <v>0.23663258843752827</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="4">
+        <v>0.76336741156247168</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B44" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" s="1">
+        <v>20350</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" s="1">
+        <v>20350</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
+  <drawing r:id="rId7"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD10136E-EE75-4F16-9358-4D1D86612DDD}">
-  <dimension ref="A3:E28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1">
-        <v>49560</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="1">
-        <v>56690</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1">
-        <v>55200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="1">
-        <v>59610</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B8" s="1">
-        <v>221060</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E9" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E10" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E11" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E12" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E13" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C14" t="s">
-        <v>122</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="1">
-        <v>15600</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="1">
-        <v>6960</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="1">
-        <v>29750</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="1">
-        <v>61200</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="1">
-        <v>24000</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="1">
-        <v>43200</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="1">
-        <v>18750</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="1">
-        <v>21600</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C23" s="1">
-        <v>221060</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E24" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E25" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E26" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E27" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E28" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K121"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
